--- a/doc/SourceData.xlsx
+++ b/doc/SourceData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YH.CHIU\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SourceCode\python\ProductionSimulatorDynamic\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767C09B5-11BD-4FA9-8A59-F61ADA590CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4132986-4FDA-4B91-B014-0F496F06799A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{42FB03BA-B493-4523-AFA3-A29D55EE9891}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{42FB03BA-B493-4523-AFA3-A29D55EE9891}"/>
   </bookViews>
   <sheets>
     <sheet name="黃光CT總表" sheetId="2" r:id="rId1"/>
@@ -1154,7 +1154,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3431" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3431" uniqueCount="645">
   <si>
     <t>片材長邊尺寸 (mm) mm</t>
   </si>
@@ -3495,6 +3495,14 @@
   </si>
   <si>
     <t>康代-AOI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UPSC040</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UPSC041</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5032,38 +5040,140 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5092,6 +5202,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5101,140 +5214,35 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -6331,21 +6339,21 @@
       </c>
     </row>
     <row r="8" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G8" s="193" t="s">
+      <c r="G8" s="251" t="s">
         <v>121</v>
       </c>
-      <c r="H8" s="194"/>
-      <c r="I8" s="195"/>
-      <c r="J8" s="196" t="s">
+      <c r="H8" s="252"/>
+      <c r="I8" s="253"/>
+      <c r="J8" s="254" t="s">
         <v>120</v>
       </c>
-      <c r="K8" s="196"/>
-      <c r="L8" s="196"/>
-      <c r="M8" s="197" t="s">
+      <c r="K8" s="254"/>
+      <c r="L8" s="254"/>
+      <c r="M8" s="255" t="s">
         <v>119</v>
       </c>
-      <c r="N8" s="197"/>
-      <c r="O8" s="197"/>
+      <c r="N8" s="255"/>
+      <c r="O8" s="255"/>
       <c r="P8" s="2"/>
     </row>
     <row r="9" spans="2:17" ht="51.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -6399,7 +6407,7 @@
       </c>
     </row>
     <row r="10" spans="2:17" ht="106.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="204" t="s">
+      <c r="B10" s="238" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="85" t="s">
@@ -6452,14 +6460,14 @@
       <c r="Q10" s="13"/>
     </row>
     <row r="11" spans="2:17" ht="84.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="205"/>
-      <c r="C11" s="207" t="s">
+      <c r="B11" s="239"/>
+      <c r="C11" s="241" t="s">
         <v>76</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="E11" s="209">
+      <c r="E11" s="243">
         <v>1</v>
       </c>
       <c r="F11" s="14" t="s">
@@ -6505,12 +6513,12 @@
       <c r="Q11" s="19"/>
     </row>
     <row r="12" spans="2:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="205"/>
-      <c r="C12" s="208"/>
+      <c r="B12" s="239"/>
+      <c r="C12" s="242"/>
       <c r="D12" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="E12" s="210"/>
+      <c r="E12" s="244"/>
       <c r="F12" s="14" t="s">
         <v>14</v>
       </c>
@@ -6554,14 +6562,14 @@
       <c r="Q12" s="19"/>
     </row>
     <row r="13" spans="2:17" ht="90.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="205"/>
-      <c r="C13" s="211" t="s">
+      <c r="B13" s="239"/>
+      <c r="C13" s="245" t="s">
         <v>109</v>
       </c>
       <c r="D13" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="213">
+      <c r="E13" s="248">
         <v>3</v>
       </c>
       <c r="F13" s="20" t="s">
@@ -6592,16 +6600,16 @@
         <f t="shared" ref="O13:O25" si="1">M13*N13/60</f>
         <v>12</v>
       </c>
-      <c r="P13" s="216"/>
-      <c r="Q13" s="217"/>
+      <c r="P13" s="224"/>
+      <c r="Q13" s="230"/>
     </row>
     <row r="14" spans="2:17" ht="90.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="205"/>
-      <c r="C14" s="212"/>
+      <c r="B14" s="239"/>
+      <c r="C14" s="246"/>
       <c r="D14" s="42" t="s">
         <v>475</v>
       </c>
-      <c r="E14" s="214"/>
+      <c r="E14" s="249"/>
       <c r="F14" s="20"/>
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
@@ -6621,16 +6629,16 @@
       <c r="M14" s="9"/>
       <c r="N14" s="10"/>
       <c r="O14" s="11"/>
-      <c r="P14" s="216"/>
-      <c r="Q14" s="217"/>
+      <c r="P14" s="224"/>
+      <c r="Q14" s="230"/>
     </row>
     <row r="15" spans="2:17" ht="90.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="205"/>
-      <c r="C15" s="201"/>
+      <c r="B15" s="239"/>
+      <c r="C15" s="247"/>
       <c r="D15" s="98" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="215"/>
+      <c r="E15" s="250"/>
       <c r="F15" s="20" t="s">
         <v>18</v>
       </c>
@@ -6668,11 +6676,11 @@
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="P15" s="216"/>
-      <c r="Q15" s="217"/>
+      <c r="P15" s="224"/>
+      <c r="Q15" s="230"/>
     </row>
     <row r="16" spans="2:17" ht="100.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="205"/>
+      <c r="B16" s="239"/>
       <c r="C16" s="21" t="s">
         <v>79</v>
       </c>
@@ -6722,7 +6730,7 @@
       </c>
     </row>
     <row r="17" spans="2:18" ht="98.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="206"/>
+      <c r="B17" s="240"/>
       <c r="C17" s="105" t="s">
         <v>80</v>
       </c>
@@ -6777,7 +6785,7 @@
       <c r="Q17" s="31"/>
     </row>
     <row r="18" spans="2:18" ht="122.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="253" t="s">
+      <c r="B18" s="193" t="s">
         <v>21</v>
       </c>
       <c r="C18" s="10" t="s">
@@ -6832,7 +6840,7 @@
       <c r="Q18" s="34"/>
     </row>
     <row r="19" spans="2:18" ht="57" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="254"/>
+      <c r="B19" s="194"/>
       <c r="C19" s="35" t="s">
         <v>83</v>
       </c>
@@ -6886,14 +6894,14 @@
       <c r="R19" s="37"/>
     </row>
     <row r="20" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="254"/>
+      <c r="B20" s="194"/>
       <c r="C20" s="10" t="s">
         <v>105</v>
       </c>
       <c r="D20" s="88" t="s">
         <v>106</v>
       </c>
-      <c r="E20" s="218">
+      <c r="E20" s="231">
         <v>1</v>
       </c>
       <c r="F20" s="38" t="s">
@@ -6935,19 +6943,19 @@
         <f t="shared" si="1"/>
         <v>1.25</v>
       </c>
-      <c r="P20" s="221"/>
-      <c r="Q20" s="223"/>
+      <c r="P20" s="233"/>
+      <c r="Q20" s="235"/>
       <c r="R20" s="41"/>
     </row>
     <row r="21" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="254"/>
+      <c r="B21" s="194"/>
       <c r="C21" s="10" t="s">
         <v>105</v>
       </c>
       <c r="D21" s="110" t="s">
         <v>132</v>
       </c>
-      <c r="E21" s="219"/>
+      <c r="E21" s="232"/>
       <c r="F21" s="20" t="s">
         <v>25</v>
       </c>
@@ -6978,19 +6986,19 @@
         <f>M21*N21/60</f>
         <v>1.25</v>
       </c>
-      <c r="P21" s="216"/>
-      <c r="Q21" s="224"/>
+      <c r="P21" s="224"/>
+      <c r="Q21" s="236"/>
       <c r="R21" s="41"/>
     </row>
     <row r="22" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="254"/>
+      <c r="B22" s="194"/>
       <c r="C22" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="260" t="s">
+      <c r="D22" s="210" t="s">
         <v>107</v>
       </c>
-      <c r="E22" s="219"/>
+      <c r="E22" s="232"/>
       <c r="F22" s="43" t="s">
         <v>26</v>
       </c>
@@ -7030,17 +7038,17 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="P22" s="216"/>
-      <c r="Q22" s="224"/>
+      <c r="P22" s="224"/>
+      <c r="Q22" s="236"/>
       <c r="R22" s="41"/>
     </row>
     <row r="23" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="254"/>
+      <c r="B23" s="194"/>
       <c r="C23" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D23" s="230"/>
-      <c r="E23" s="220"/>
+      <c r="D23" s="211"/>
+      <c r="E23" s="217"/>
       <c r="F23" s="47" t="s">
         <v>24</v>
       </c>
@@ -7080,12 +7088,12 @@
         <f t="shared" si="1"/>
         <v>1.25</v>
       </c>
-      <c r="P23" s="222"/>
-      <c r="Q23" s="225"/>
+      <c r="P23" s="234"/>
+      <c r="Q23" s="237"/>
       <c r="R23" s="41"/>
     </row>
     <row r="24" spans="2:18" ht="133.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="255"/>
+      <c r="B24" s="195"/>
       <c r="C24" s="91" t="s">
         <v>84</v>
       </c>
@@ -7139,29 +7147,29 @@
       <c r="R24" s="49"/>
     </row>
     <row r="25" spans="2:18" ht="129" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="228" t="s">
+      <c r="B25" s="214" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="236" t="s">
+      <c r="C25" s="200" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="236" t="s">
+      <c r="D25" s="200" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="237">
+      <c r="E25" s="222">
         <v>1</v>
       </c>
       <c r="F25" s="50" t="s">
         <v>140</v>
       </c>
-      <c r="G25" s="202">
+      <c r="G25" s="259">
         <f>90/4</f>
         <v>22.5</v>
       </c>
-      <c r="H25" s="200">
+      <c r="H25" s="258">
         <v>8</v>
       </c>
-      <c r="I25" s="198">
+      <c r="I25" s="256">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
@@ -7177,14 +7185,14 @@
         <f t="shared" si="4"/>
         <v>3.75</v>
       </c>
-      <c r="M25" s="198">
+      <c r="M25" s="256">
         <f>90/5</f>
         <v>18</v>
       </c>
-      <c r="N25" s="200">
+      <c r="N25" s="258">
         <v>10</v>
       </c>
-      <c r="O25" s="198">
+      <c r="O25" s="256">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -7192,16 +7200,16 @@
       <c r="Q25" s="51"/>
     </row>
     <row r="26" spans="2:18" ht="136.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="228"/>
-      <c r="C26" s="236"/>
-      <c r="D26" s="236"/>
-      <c r="E26" s="238"/>
+      <c r="B26" s="214"/>
+      <c r="C26" s="200"/>
+      <c r="D26" s="200"/>
+      <c r="E26" s="223"/>
       <c r="F26" s="48" t="s">
         <v>141</v>
       </c>
-      <c r="G26" s="203"/>
-      <c r="H26" s="201"/>
-      <c r="I26" s="199"/>
+      <c r="G26" s="260"/>
+      <c r="H26" s="247"/>
+      <c r="I26" s="257"/>
       <c r="J26" s="15">
         <f>110/4</f>
         <v>27.5</v>
@@ -7214,21 +7222,21 @@
         <f t="shared" ref="L26" si="7">J26*K26/60</f>
         <v>4.583333333333333</v>
       </c>
-      <c r="M26" s="199"/>
-      <c r="N26" s="201"/>
-      <c r="O26" s="199"/>
+      <c r="M26" s="257"/>
+      <c r="N26" s="247"/>
+      <c r="O26" s="257"/>
       <c r="P26" s="141"/>
       <c r="Q26" s="23"/>
     </row>
     <row r="27" spans="2:18" ht="73.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="228"/>
+      <c r="B27" s="214"/>
       <c r="C27" s="142" t="s">
         <v>139</v>
       </c>
-      <c r="D27" s="229" t="s">
+      <c r="D27" s="215" t="s">
         <v>90</v>
       </c>
-      <c r="E27" s="231">
+      <c r="E27" s="216">
         <v>1</v>
       </c>
       <c r="F27" s="47" t="s">
@@ -7270,16 +7278,16 @@
         <f>M27*N27/60</f>
         <v>0.8666666666666667</v>
       </c>
-      <c r="P27" s="232"/>
-      <c r="Q27" s="226"/>
+      <c r="P27" s="218"/>
+      <c r="Q27" s="212"/>
     </row>
     <row r="28" spans="2:18" ht="73.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="228"/>
+      <c r="B28" s="214"/>
       <c r="C28" s="52" t="s">
         <v>138</v>
       </c>
-      <c r="D28" s="230"/>
-      <c r="E28" s="220"/>
+      <c r="D28" s="211"/>
+      <c r="E28" s="217"/>
       <c r="F28" s="32" t="s">
         <v>89</v>
       </c>
@@ -7316,11 +7324,11 @@
         <f>M28*N28/60</f>
         <v>13</v>
       </c>
-      <c r="P28" s="233"/>
-      <c r="Q28" s="227"/>
+      <c r="P28" s="219"/>
+      <c r="Q28" s="213"/>
     </row>
     <row r="29" spans="2:18" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
+      <c r="B29" s="214"/>
       <c r="C29" s="35" t="s">
         <v>91</v>
       </c>
@@ -7373,7 +7381,7 @@
       <c r="Q29" s="31"/>
     </row>
     <row r="30" spans="2:18" ht="53.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
+      <c r="B30" s="214"/>
       <c r="C30" s="55" t="s">
         <v>92</v>
       </c>
@@ -7426,14 +7434,14 @@
       <c r="Q30" s="58"/>
     </row>
     <row r="31" spans="2:18" ht="53.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="259" t="s">
+      <c r="B31" s="214"/>
+      <c r="C31" s="199" t="s">
         <v>93</v>
       </c>
-      <c r="D31" s="236" t="s">
+      <c r="D31" s="200" t="s">
         <v>32</v>
       </c>
-      <c r="E31" s="256">
+      <c r="E31" s="196">
         <v>1</v>
       </c>
       <c r="F31" s="14" t="s">
@@ -7473,10 +7481,10 @@
       <c r="Q31" s="60"/>
     </row>
     <row r="32" spans="2:18" ht="53.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="228"/>
-      <c r="C32" s="259"/>
-      <c r="D32" s="236"/>
-      <c r="E32" s="257"/>
+      <c r="B32" s="214"/>
+      <c r="C32" s="199"/>
+      <c r="D32" s="200"/>
+      <c r="E32" s="197"/>
       <c r="F32" s="14" t="s">
         <v>34</v>
       </c>
@@ -7514,10 +7522,10 @@
       <c r="Q32" s="60"/>
     </row>
     <row r="33" spans="2:17" ht="53.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="228"/>
-      <c r="C33" s="259"/>
-      <c r="D33" s="236"/>
-      <c r="E33" s="258"/>
+      <c r="B33" s="214"/>
+      <c r="C33" s="199"/>
+      <c r="D33" s="200"/>
+      <c r="E33" s="198"/>
       <c r="F33" s="14" t="s">
         <v>35</v>
       </c>
@@ -7555,14 +7563,14 @@
       <c r="Q33" s="60"/>
     </row>
     <row r="34" spans="2:17" ht="52.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="228"/>
-      <c r="C34" s="259" t="s">
+      <c r="B34" s="214"/>
+      <c r="C34" s="199" t="s">
         <v>96</v>
       </c>
-      <c r="D34" s="236" t="s">
+      <c r="D34" s="200" t="s">
         <v>36</v>
       </c>
-      <c r="E34" s="244">
+      <c r="E34" s="201">
         <v>1</v>
       </c>
       <c r="F34" s="61" t="s">
@@ -7601,10 +7609,10 @@
       <c r="Q34" s="31"/>
     </row>
     <row r="35" spans="2:17" ht="52.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="228"/>
-      <c r="C35" s="259"/>
-      <c r="D35" s="236"/>
-      <c r="E35" s="244"/>
+      <c r="B35" s="214"/>
+      <c r="C35" s="199"/>
+      <c r="D35" s="200"/>
+      <c r="E35" s="201"/>
       <c r="F35" s="61" t="s">
         <v>135</v>
       </c>
@@ -7645,7 +7653,7 @@
       <c r="Q35" s="31"/>
     </row>
     <row r="36" spans="2:17" s="113" customFormat="1" ht="90.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="228"/>
+      <c r="B36" s="214"/>
       <c r="C36" s="139" t="s">
         <v>97</v>
       </c>
@@ -7695,14 +7703,14 @@
       <c r="Q36" s="126"/>
     </row>
     <row r="37" spans="2:17" ht="81" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="228"/>
-      <c r="C37" s="251" t="s">
+      <c r="B37" s="214"/>
+      <c r="C37" s="208" t="s">
         <v>109</v>
       </c>
       <c r="D37" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="E37" s="234">
+      <c r="E37" s="220">
         <v>3</v>
       </c>
       <c r="F37" s="56" t="s">
@@ -7744,18 +7752,18 @@
         <f>M37*N37/60</f>
         <v>12.5</v>
       </c>
-      <c r="P37" s="216"/>
-      <c r="Q37" s="240" t="s">
+      <c r="P37" s="224"/>
+      <c r="Q37" s="226" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="38" spans="2:17" ht="81" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="228"/>
-      <c r="C38" s="252"/>
+      <c r="B38" s="214"/>
+      <c r="C38" s="209"/>
       <c r="D38" s="88" t="s">
         <v>42</v>
       </c>
-      <c r="E38" s="235"/>
+      <c r="E38" s="221"/>
       <c r="F38" s="56" t="s">
         <v>43</v>
       </c>
@@ -7795,18 +7803,18 @@
         <f>M38*N38/60</f>
         <v>5</v>
       </c>
-      <c r="P38" s="216"/>
-      <c r="Q38" s="241"/>
+      <c r="P38" s="224"/>
+      <c r="Q38" s="227"/>
     </row>
     <row r="39" spans="2:17" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="228"/>
+      <c r="B39" s="214"/>
       <c r="C39" s="62" t="s">
         <v>103</v>
       </c>
       <c r="D39" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="E39" s="235"/>
+      <c r="E39" s="221"/>
       <c r="F39" s="56" t="s">
         <v>45</v>
       </c>
@@ -7846,20 +7854,20 @@
         <f>M39*N39/60</f>
         <v>1.25</v>
       </c>
-      <c r="P39" s="216"/>
-      <c r="Q39" s="242" t="s">
+      <c r="P39" s="224"/>
+      <c r="Q39" s="228" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="40" spans="2:17" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="228"/>
+      <c r="B40" s="214"/>
       <c r="C40" s="55" t="s">
         <v>103</v>
       </c>
       <c r="D40" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="E40" s="235"/>
+      <c r="E40" s="221"/>
       <c r="F40" s="56" t="s">
         <v>48</v>
       </c>
@@ -7899,11 +7907,11 @@
         <f>M40*N40/60</f>
         <v>0.625</v>
       </c>
-      <c r="P40" s="239"/>
-      <c r="Q40" s="243"/>
+      <c r="P40" s="225"/>
+      <c r="Q40" s="229"/>
     </row>
     <row r="41" spans="2:17" ht="64.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="253" t="s">
+      <c r="B41" s="193" t="s">
         <v>49</v>
       </c>
       <c r="C41" s="9" t="s">
@@ -7912,7 +7920,7 @@
       <c r="D41" s="94" t="s">
         <v>50</v>
       </c>
-      <c r="E41" s="244">
+      <c r="E41" s="201">
         <v>2</v>
       </c>
       <c r="F41" s="63" t="s">
@@ -7960,14 +7968,14 @@
       <c r="Q41" s="59"/>
     </row>
     <row r="42" spans="2:17" ht="64.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="254"/>
+      <c r="B42" s="194"/>
       <c r="C42" s="9" t="s">
         <v>111</v>
       </c>
       <c r="D42" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="E42" s="244"/>
+      <c r="E42" s="201"/>
       <c r="F42" s="63" t="s">
         <v>54</v>
       </c>
@@ -8013,7 +8021,7 @@
       <c r="Q42" s="66"/>
     </row>
     <row r="43" spans="2:17" ht="64.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="254"/>
+      <c r="B43" s="194"/>
       <c r="C43" s="120" t="s">
         <v>112</v>
       </c>
@@ -8065,7 +8073,7 @@
       <c r="Q43" s="121"/>
     </row>
     <row r="44" spans="2:17" ht="324.60000000000002" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="254"/>
+      <c r="B44" s="194"/>
       <c r="C44" s="9" t="s">
         <v>98</v>
       </c>
@@ -8118,7 +8126,7 @@
       <c r="Q44" s="68"/>
     </row>
     <row r="45" spans="2:17" ht="97.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="254"/>
+      <c r="B45" s="194"/>
       <c r="C45" s="35" t="s">
         <v>99</v>
       </c>
@@ -8171,14 +8179,14 @@
       <c r="Q45" s="51"/>
     </row>
     <row r="46" spans="2:17" ht="63.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="254"/>
-      <c r="C46" s="245" t="s">
+      <c r="B46" s="194"/>
+      <c r="C46" s="202" t="s">
         <v>100</v>
       </c>
-      <c r="D46" s="248" t="s">
+      <c r="D46" s="205" t="s">
         <v>62</v>
       </c>
-      <c r="E46" s="256">
+      <c r="E46" s="196">
         <v>1</v>
       </c>
       <c r="F46" s="14" t="s">
@@ -8224,10 +8232,10 @@
       <c r="Q46" s="69"/>
     </row>
     <row r="47" spans="2:17" ht="63.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="254"/>
-      <c r="C47" s="246"/>
-      <c r="D47" s="249"/>
-      <c r="E47" s="257"/>
+      <c r="B47" s="194"/>
+      <c r="C47" s="203"/>
+      <c r="D47" s="206"/>
+      <c r="E47" s="197"/>
       <c r="F47" s="14" t="s">
         <v>64</v>
       </c>
@@ -8271,10 +8279,10 @@
       <c r="Q47" s="69"/>
     </row>
     <row r="48" spans="2:17" ht="63.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="254"/>
-      <c r="C48" s="247"/>
-      <c r="D48" s="250"/>
-      <c r="E48" s="258"/>
+      <c r="B48" s="194"/>
+      <c r="C48" s="204"/>
+      <c r="D48" s="207"/>
+      <c r="E48" s="198"/>
       <c r="F48" s="14" t="s">
         <v>65</v>
       </c>
@@ -8315,7 +8323,7 @@
       <c r="Q48" s="69"/>
     </row>
     <row r="49" spans="2:17" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="254"/>
+      <c r="B49" s="194"/>
       <c r="C49" s="35" t="s">
         <v>101</v>
       </c>
@@ -8368,7 +8376,7 @@
       <c r="Q49" s="71"/>
     </row>
     <row r="50" spans="2:17" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="255"/>
+      <c r="B50" s="195"/>
       <c r="C50" s="9" t="s">
         <v>102</v>
       </c>
@@ -8418,7 +8426,7 @@
       <c r="Q50" s="72"/>
     </row>
     <row r="51" spans="2:17" ht="88.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="253" t="s">
+      <c r="B51" s="193" t="s">
         <v>69</v>
       </c>
       <c r="C51" s="78" t="s">
@@ -8473,7 +8481,7 @@
       </c>
     </row>
     <row r="52" spans="2:17" ht="93.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="254"/>
+      <c r="B52" s="194"/>
       <c r="C52" s="21" t="s">
         <v>123</v>
       </c>
@@ -8523,7 +8531,7 @@
       <c r="Q52" s="30"/>
     </row>
     <row r="53" spans="2:17" ht="93.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="254"/>
+      <c r="B53" s="194"/>
       <c r="C53" s="21" t="s">
         <v>123</v>
       </c>
@@ -8573,7 +8581,7 @@
       </c>
     </row>
     <row r="54" spans="2:17" ht="71.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="254"/>
+      <c r="B54" s="194"/>
       <c r="C54" s="21" t="s">
         <v>113</v>
       </c>
@@ -8621,7 +8629,7 @@
       <c r="Q54" s="76"/>
     </row>
     <row r="55" spans="2:17" s="113" customFormat="1" ht="77.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="255"/>
+      <c r="B55" s="195"/>
       <c r="C55" s="114" t="s">
         <v>114</v>
       </c>
@@ -8674,18 +8682,25 @@
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="B51:B55"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="M25:M26"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="O25:O26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="B10:B17"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="P13:P15"/>
+    <mergeCell ref="Q13:Q15"/>
+    <mergeCell ref="E20:E23"/>
+    <mergeCell ref="P20:P23"/>
+    <mergeCell ref="Q20:Q23"/>
     <mergeCell ref="B18:B24"/>
     <mergeCell ref="B41:B50"/>
     <mergeCell ref="D22:D23"/>
@@ -8701,25 +8716,18 @@
     <mergeCell ref="P37:P40"/>
     <mergeCell ref="Q37:Q38"/>
     <mergeCell ref="Q39:Q40"/>
-    <mergeCell ref="P13:P15"/>
-    <mergeCell ref="Q13:Q15"/>
-    <mergeCell ref="E20:E23"/>
-    <mergeCell ref="P20:P23"/>
-    <mergeCell ref="Q20:Q23"/>
-    <mergeCell ref="B10:B17"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="M25:M26"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="O25:O26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="B51:B55"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="C37:C38"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11171,7 +11179,7 @@
         <v>638</v>
       </c>
       <c r="F18" s="188">
-        <v>12.166666666666666</v>
+        <v>2</v>
       </c>
       <c r="G18" s="149">
         <v>7.8</v>
@@ -11321,7 +11329,7 @@
         <v>639</v>
       </c>
       <c r="F20" s="188">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="G20" s="155">
         <v>1</v>
@@ -12829,7 +12837,7 @@
         <v>638</v>
       </c>
       <c r="F40" s="188">
-        <v>12.166666666666666</v>
+        <v>2</v>
       </c>
       <c r="G40" s="149">
         <v>7.8</v>
@@ -13054,7 +13062,7 @@
         <v>639</v>
       </c>
       <c r="F43" s="188">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="G43" s="155">
         <v>1</v>
@@ -14821,7 +14829,7 @@
         <v>638</v>
       </c>
       <c r="F66" s="188">
-        <v>12.166666666666666</v>
+        <v>2</v>
       </c>
       <c r="G66" s="149">
         <v>0.5</v>
@@ -14896,7 +14904,7 @@
         <v>638</v>
       </c>
       <c r="F67" s="188">
-        <v>12.166666666666666</v>
+        <v>2</v>
       </c>
       <c r="G67" s="149">
         <v>0.8</v>
@@ -16329,7 +16337,7 @@
         <v>638</v>
       </c>
       <c r="F86" s="188">
-        <v>12.166666666666666</v>
+        <v>2</v>
       </c>
       <c r="G86" s="149">
         <v>0.8</v>
@@ -19001,7 +19009,7 @@
         <v>163</v>
       </c>
       <c r="C121" s="182" t="s">
-        <v>405</v>
+        <v>643</v>
       </c>
       <c r="D121" s="185" t="s">
         <v>406</v>
@@ -19076,7 +19084,7 @@
         <v>163</v>
       </c>
       <c r="C122" s="182" t="s">
-        <v>407</v>
+        <v>644</v>
       </c>
       <c r="D122" s="185" t="s">
         <v>408</v>
@@ -19085,7 +19093,7 @@
         <v>638</v>
       </c>
       <c r="F122" s="188">
-        <v>12.166666666666666</v>
+        <v>2</v>
       </c>
       <c r="G122" s="149">
         <v>9.8000000000000007</v>
@@ -19310,7 +19318,7 @@
         <v>639</v>
       </c>
       <c r="F125" s="188">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="G125" s="155">
         <v>1</v>

--- a/doc/SourceData.xlsx
+++ b/doc/SourceData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SourceCode\python\ProductionSimulatorDynamic\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152A5BC5-E66F-4723-826D-AD9E382216A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE4E8F7-4715-4742-BEC0-0308A151ECFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{42FB03BA-B493-4523-AFA3-A29D55EE9891}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{42FB03BA-B493-4523-AFA3-A29D55EE9891}"/>
   </bookViews>
   <sheets>
     <sheet name="黃光CT總表" sheetId="2" r:id="rId1"/>
@@ -1154,7 +1154,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3431" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3446" uniqueCount="648">
   <si>
     <t>片材長邊尺寸 (mm) mm</t>
   </si>
@@ -3510,6 +3510,13 @@
     <t>PR0254
 舊機改機</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>威寶通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SP0002</t>
   </si>
 </sst>
 </file>
@@ -5043,6 +5050,9 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="9" fontId="5" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5246,9 +5256,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -6345,21 +6352,21 @@
       </c>
     </row>
     <row r="8" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="G8" s="192" t="s">
+      <c r="G8" s="193" t="s">
         <v>121</v>
       </c>
-      <c r="H8" s="193"/>
-      <c r="I8" s="194"/>
-      <c r="J8" s="195" t="s">
+      <c r="H8" s="194"/>
+      <c r="I8" s="195"/>
+      <c r="J8" s="196" t="s">
         <v>120</v>
       </c>
-      <c r="K8" s="195"/>
-      <c r="L8" s="195"/>
-      <c r="M8" s="196" t="s">
+      <c r="K8" s="196"/>
+      <c r="L8" s="196"/>
+      <c r="M8" s="197" t="s">
         <v>119</v>
       </c>
-      <c r="N8" s="196"/>
-      <c r="O8" s="196"/>
+      <c r="N8" s="197"/>
+      <c r="O8" s="197"/>
       <c r="P8" s="2"/>
     </row>
     <row r="9" spans="2:17" ht="51.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6413,7 +6420,7 @@
       </c>
     </row>
     <row r="10" spans="2:17" ht="106.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="203" t="s">
+      <c r="B10" s="204" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="85" t="s">
@@ -6466,14 +6473,14 @@
       <c r="Q10" s="13"/>
     </row>
     <row r="11" spans="2:17" ht="84.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="204"/>
-      <c r="C11" s="206" t="s">
+      <c r="B11" s="205"/>
+      <c r="C11" s="207" t="s">
         <v>76</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="E11" s="208">
+      <c r="E11" s="209">
         <v>1</v>
       </c>
       <c r="F11" s="14" t="s">
@@ -6519,12 +6526,12 @@
       <c r="Q11" s="19"/>
     </row>
     <row r="12" spans="2:17" ht="86.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="204"/>
-      <c r="C12" s="207"/>
+      <c r="B12" s="205"/>
+      <c r="C12" s="208"/>
       <c r="D12" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="E12" s="209"/>
+      <c r="E12" s="210"/>
       <c r="F12" s="14" t="s">
         <v>14</v>
       </c>
@@ -6568,14 +6575,14 @@
       <c r="Q12" s="19"/>
     </row>
     <row r="13" spans="2:17" ht="90.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="204"/>
-      <c r="C13" s="210" t="s">
+      <c r="B13" s="205"/>
+      <c r="C13" s="211" t="s">
         <v>109</v>
       </c>
       <c r="D13" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="212">
+      <c r="E13" s="213">
         <v>3</v>
       </c>
       <c r="F13" s="20" t="s">
@@ -6606,16 +6613,16 @@
         <f t="shared" ref="O13:O25" si="1">M13*N13/60</f>
         <v>12</v>
       </c>
-      <c r="P13" s="215"/>
-      <c r="Q13" s="216"/>
+      <c r="P13" s="216"/>
+      <c r="Q13" s="217"/>
     </row>
     <row r="14" spans="2:17" ht="90.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="204"/>
-      <c r="C14" s="211"/>
+      <c r="B14" s="205"/>
+      <c r="C14" s="212"/>
       <c r="D14" s="42" t="s">
         <v>474</v>
       </c>
-      <c r="E14" s="213"/>
+      <c r="E14" s="214"/>
       <c r="F14" s="20"/>
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
@@ -6635,16 +6642,16 @@
       <c r="M14" s="9"/>
       <c r="N14" s="10"/>
       <c r="O14" s="11"/>
-      <c r="P14" s="215"/>
-      <c r="Q14" s="216"/>
+      <c r="P14" s="216"/>
+      <c r="Q14" s="217"/>
     </row>
     <row r="15" spans="2:17" ht="90.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="204"/>
-      <c r="C15" s="200"/>
+      <c r="B15" s="205"/>
+      <c r="C15" s="201"/>
       <c r="D15" s="98" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="214"/>
+      <c r="E15" s="215"/>
       <c r="F15" s="20" t="s">
         <v>18</v>
       </c>
@@ -6682,11 +6689,11 @@
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="P15" s="215"/>
-      <c r="Q15" s="216"/>
+      <c r="P15" s="216"/>
+      <c r="Q15" s="217"/>
     </row>
     <row r="16" spans="2:17" ht="100.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="204"/>
+      <c r="B16" s="205"/>
       <c r="C16" s="21" t="s">
         <v>79</v>
       </c>
@@ -6736,7 +6743,7 @@
       </c>
     </row>
     <row r="17" spans="2:18" ht="98.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="205"/>
+      <c r="B17" s="206"/>
       <c r="C17" s="105" t="s">
         <v>80</v>
       </c>
@@ -6791,7 +6798,7 @@
       <c r="Q17" s="31"/>
     </row>
     <row r="18" spans="2:18" ht="122.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="225" t="s">
+      <c r="B18" s="226" t="s">
         <v>21</v>
       </c>
       <c r="C18" s="10" t="s">
@@ -6846,7 +6853,7 @@
       <c r="Q18" s="34"/>
     </row>
     <row r="19" spans="2:18" ht="57" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="226"/>
+      <c r="B19" s="227"/>
       <c r="C19" s="35" t="s">
         <v>83</v>
       </c>
@@ -6900,14 +6907,14 @@
       <c r="R19" s="37"/>
     </row>
     <row r="20" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="226"/>
+      <c r="B20" s="227"/>
       <c r="C20" s="10" t="s">
         <v>105</v>
       </c>
       <c r="D20" s="88" t="s">
         <v>106</v>
       </c>
-      <c r="E20" s="217">
+      <c r="E20" s="218">
         <v>1</v>
       </c>
       <c r="F20" s="38" t="s">
@@ -6949,19 +6956,19 @@
         <f t="shared" si="1"/>
         <v>1.25</v>
       </c>
-      <c r="P20" s="220"/>
-      <c r="Q20" s="222"/>
+      <c r="P20" s="221"/>
+      <c r="Q20" s="223"/>
       <c r="R20" s="41"/>
     </row>
     <row r="21" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="226"/>
+      <c r="B21" s="227"/>
       <c r="C21" s="10" t="s">
         <v>105</v>
       </c>
       <c r="D21" s="110" t="s">
         <v>132</v>
       </c>
-      <c r="E21" s="218"/>
+      <c r="E21" s="219"/>
       <c r="F21" s="20" t="s">
         <v>25</v>
       </c>
@@ -6992,19 +6999,19 @@
         <f>M21*N21/60</f>
         <v>1.25</v>
       </c>
-      <c r="P21" s="215"/>
-      <c r="Q21" s="223"/>
+      <c r="P21" s="216"/>
+      <c r="Q21" s="224"/>
       <c r="R21" s="41"/>
     </row>
     <row r="22" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="226"/>
+      <c r="B22" s="227"/>
       <c r="C22" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="228" t="s">
+      <c r="D22" s="229" t="s">
         <v>107</v>
       </c>
-      <c r="E22" s="218"/>
+      <c r="E22" s="219"/>
       <c r="F22" s="43" t="s">
         <v>26</v>
       </c>
@@ -7044,17 +7051,17 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="P22" s="215"/>
-      <c r="Q22" s="223"/>
+      <c r="P22" s="216"/>
+      <c r="Q22" s="224"/>
       <c r="R22" s="41"/>
     </row>
     <row r="23" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="226"/>
+      <c r="B23" s="227"/>
       <c r="C23" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D23" s="229"/>
-      <c r="E23" s="219"/>
+      <c r="D23" s="230"/>
+      <c r="E23" s="220"/>
       <c r="F23" s="47" t="s">
         <v>24</v>
       </c>
@@ -7094,12 +7101,12 @@
         <f t="shared" si="1"/>
         <v>1.25</v>
       </c>
-      <c r="P23" s="221"/>
-      <c r="Q23" s="224"/>
+      <c r="P23" s="222"/>
+      <c r="Q23" s="225"/>
       <c r="R23" s="41"/>
     </row>
     <row r="24" spans="2:18" ht="133.19999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="227"/>
+      <c r="B24" s="228"/>
       <c r="C24" s="91" t="s">
         <v>84</v>
       </c>
@@ -7153,29 +7160,29 @@
       <c r="R24" s="49"/>
     </row>
     <row r="25" spans="2:18" ht="129" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="232" t="s">
+      <c r="B25" s="233" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="239" t="s">
+      <c r="C25" s="240" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="239" t="s">
+      <c r="D25" s="240" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="240">
+      <c r="E25" s="241">
         <v>1</v>
       </c>
       <c r="F25" s="50" t="s">
         <v>140</v>
       </c>
-      <c r="G25" s="201">
+      <c r="G25" s="202">
         <f>90/4</f>
         <v>22.5</v>
       </c>
-      <c r="H25" s="199">
+      <c r="H25" s="200">
         <v>8</v>
       </c>
-      <c r="I25" s="197">
+      <c r="I25" s="198">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
@@ -7191,14 +7198,14 @@
         <f t="shared" si="4"/>
         <v>3.75</v>
       </c>
-      <c r="M25" s="197">
+      <c r="M25" s="198">
         <f>90/5</f>
         <v>18</v>
       </c>
-      <c r="N25" s="199">
+      <c r="N25" s="200">
         <v>10</v>
       </c>
-      <c r="O25" s="197">
+      <c r="O25" s="198">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -7206,16 +7213,16 @@
       <c r="Q25" s="51"/>
     </row>
     <row r="26" spans="2:18" ht="136.19999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="232"/>
-      <c r="C26" s="239"/>
-      <c r="D26" s="239"/>
-      <c r="E26" s="241"/>
+      <c r="B26" s="233"/>
+      <c r="C26" s="240"/>
+      <c r="D26" s="240"/>
+      <c r="E26" s="242"/>
       <c r="F26" s="48" t="s">
         <v>141</v>
       </c>
-      <c r="G26" s="202"/>
-      <c r="H26" s="200"/>
-      <c r="I26" s="198"/>
+      <c r="G26" s="203"/>
+      <c r="H26" s="201"/>
+      <c r="I26" s="199"/>
       <c r="J26" s="15">
         <f>110/4</f>
         <v>27.5</v>
@@ -7228,21 +7235,21 @@
         <f t="shared" ref="L26" si="7">J26*K26/60</f>
         <v>4.583333333333333</v>
       </c>
-      <c r="M26" s="198"/>
-      <c r="N26" s="200"/>
-      <c r="O26" s="198"/>
+      <c r="M26" s="199"/>
+      <c r="N26" s="201"/>
+      <c r="O26" s="199"/>
       <c r="P26" s="140"/>
       <c r="Q26" s="23"/>
     </row>
     <row r="27" spans="2:18" ht="73.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="232"/>
+      <c r="B27" s="233"/>
       <c r="C27" s="141" t="s">
         <v>139</v>
       </c>
-      <c r="D27" s="233" t="s">
+      <c r="D27" s="234" t="s">
         <v>90</v>
       </c>
-      <c r="E27" s="234">
+      <c r="E27" s="235">
         <v>1</v>
       </c>
       <c r="F27" s="47" t="s">
@@ -7284,16 +7291,16 @@
         <f>M27*N27/60</f>
         <v>0.8666666666666667</v>
       </c>
-      <c r="P27" s="235"/>
-      <c r="Q27" s="230"/>
+      <c r="P27" s="236"/>
+      <c r="Q27" s="231"/>
     </row>
     <row r="28" spans="2:18" ht="73.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="232"/>
+      <c r="B28" s="233"/>
       <c r="C28" s="52" t="s">
         <v>138</v>
       </c>
-      <c r="D28" s="229"/>
-      <c r="E28" s="219"/>
+      <c r="D28" s="230"/>
+      <c r="E28" s="220"/>
       <c r="F28" s="32" t="s">
         <v>89</v>
       </c>
@@ -7330,11 +7337,11 @@
         <f>M28*N28/60</f>
         <v>13</v>
       </c>
-      <c r="P28" s="236"/>
-      <c r="Q28" s="231"/>
+      <c r="P28" s="237"/>
+      <c r="Q28" s="232"/>
     </row>
     <row r="29" spans="2:18" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="232"/>
+      <c r="B29" s="233"/>
       <c r="C29" s="35" t="s">
         <v>91</v>
       </c>
@@ -7387,7 +7394,7 @@
       <c r="Q29" s="31"/>
     </row>
     <row r="30" spans="2:18" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="232"/>
+      <c r="B30" s="233"/>
       <c r="C30" s="55" t="s">
         <v>92</v>
       </c>
@@ -7440,14 +7447,14 @@
       <c r="Q30" s="58"/>
     </row>
     <row r="31" spans="2:18" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="232"/>
-      <c r="C31" s="250" t="s">
+      <c r="B31" s="233"/>
+      <c r="C31" s="251" t="s">
         <v>93</v>
       </c>
-      <c r="D31" s="239" t="s">
+      <c r="D31" s="240" t="s">
         <v>32</v>
       </c>
-      <c r="E31" s="247">
+      <c r="E31" s="248">
         <v>1</v>
       </c>
       <c r="F31" s="14" t="s">
@@ -7487,10 +7494,10 @@
       <c r="Q31" s="60"/>
     </row>
     <row r="32" spans="2:18" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="232"/>
-      <c r="C32" s="250"/>
-      <c r="D32" s="239"/>
-      <c r="E32" s="248"/>
+      <c r="B32" s="233"/>
+      <c r="C32" s="251"/>
+      <c r="D32" s="240"/>
+      <c r="E32" s="249"/>
       <c r="F32" s="14" t="s">
         <v>34</v>
       </c>
@@ -7528,10 +7535,10 @@
       <c r="Q32" s="60"/>
     </row>
     <row r="33" spans="2:17" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="232"/>
-      <c r="C33" s="250"/>
-      <c r="D33" s="239"/>
-      <c r="E33" s="249"/>
+      <c r="B33" s="233"/>
+      <c r="C33" s="251"/>
+      <c r="D33" s="240"/>
+      <c r="E33" s="250"/>
       <c r="F33" s="14" t="s">
         <v>35</v>
       </c>
@@ -7569,14 +7576,14 @@
       <c r="Q33" s="60"/>
     </row>
     <row r="34" spans="2:17" ht="52.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="232"/>
-      <c r="C34" s="250" t="s">
+      <c r="B34" s="233"/>
+      <c r="C34" s="251" t="s">
         <v>96</v>
       </c>
-      <c r="D34" s="239" t="s">
+      <c r="D34" s="240" t="s">
         <v>36</v>
       </c>
-      <c r="E34" s="251">
+      <c r="E34" s="252">
         <v>1</v>
       </c>
       <c r="F34" s="61" t="s">
@@ -7615,10 +7622,10 @@
       <c r="Q34" s="31"/>
     </row>
     <row r="35" spans="2:17" ht="52.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="232"/>
-      <c r="C35" s="250"/>
-      <c r="D35" s="239"/>
-      <c r="E35" s="251"/>
+      <c r="B35" s="233"/>
+      <c r="C35" s="251"/>
+      <c r="D35" s="240"/>
+      <c r="E35" s="252"/>
       <c r="F35" s="61" t="s">
         <v>135</v>
       </c>
@@ -7659,8 +7666,8 @@
       <c r="Q35" s="31"/>
     </row>
     <row r="36" spans="2:17" s="113" customFormat="1" ht="90.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="232"/>
-      <c r="C36" s="260" t="s">
+      <c r="B36" s="233"/>
+      <c r="C36" s="192" t="s">
         <v>645</v>
       </c>
       <c r="D36" s="124" t="s">
@@ -7709,14 +7716,14 @@
       <c r="Q36" s="126"/>
     </row>
     <row r="37" spans="2:17" ht="81" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="232"/>
-      <c r="C37" s="258" t="s">
+      <c r="B37" s="233"/>
+      <c r="C37" s="259" t="s">
         <v>109</v>
       </c>
       <c r="D37" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="E37" s="237">
+      <c r="E37" s="238">
         <v>3</v>
       </c>
       <c r="F37" s="56" t="s">
@@ -7758,18 +7765,18 @@
         <f>M37*N37/60</f>
         <v>12.5</v>
       </c>
-      <c r="P37" s="215"/>
-      <c r="Q37" s="243" t="s">
+      <c r="P37" s="216"/>
+      <c r="Q37" s="244" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="38" spans="2:17" ht="81" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="232"/>
-      <c r="C38" s="259"/>
+      <c r="B38" s="233"/>
+      <c r="C38" s="260"/>
       <c r="D38" s="88" t="s">
         <v>42</v>
       </c>
-      <c r="E38" s="238"/>
+      <c r="E38" s="239"/>
       <c r="F38" s="56" t="s">
         <v>43</v>
       </c>
@@ -7809,18 +7816,18 @@
         <f>M38*N38/60</f>
         <v>5</v>
       </c>
-      <c r="P38" s="215"/>
-      <c r="Q38" s="244"/>
+      <c r="P38" s="216"/>
+      <c r="Q38" s="245"/>
     </row>
     <row r="39" spans="2:17" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="232"/>
+      <c r="B39" s="233"/>
       <c r="C39" s="62" t="s">
         <v>103</v>
       </c>
       <c r="D39" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="E39" s="238"/>
+      <c r="E39" s="239"/>
       <c r="F39" s="56" t="s">
         <v>45</v>
       </c>
@@ -7860,20 +7867,20 @@
         <f>M39*N39/60</f>
         <v>1.25</v>
       </c>
-      <c r="P39" s="215"/>
-      <c r="Q39" s="245" t="s">
+      <c r="P39" s="216"/>
+      <c r="Q39" s="246" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="40" spans="2:17" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="232"/>
+      <c r="B40" s="233"/>
       <c r="C40" s="55" t="s">
         <v>103</v>
       </c>
       <c r="D40" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="E40" s="238"/>
+      <c r="E40" s="239"/>
       <c r="F40" s="56" t="s">
         <v>48</v>
       </c>
@@ -7913,11 +7920,11 @@
         <f>M40*N40/60</f>
         <v>0.625</v>
       </c>
-      <c r="P40" s="242"/>
-      <c r="Q40" s="246"/>
+      <c r="P40" s="243"/>
+      <c r="Q40" s="247"/>
     </row>
     <row r="41" spans="2:17" ht="64.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="226" t="s">
         <v>49</v>
       </c>
       <c r="C41" s="9" t="s">
@@ -7926,7 +7933,7 @@
       <c r="D41" s="94" t="s">
         <v>50</v>
       </c>
-      <c r="E41" s="251">
+      <c r="E41" s="252">
         <v>2</v>
       </c>
       <c r="F41" s="63" t="s">
@@ -7974,14 +7981,14 @@
       <c r="Q41" s="59"/>
     </row>
     <row r="42" spans="2:17" ht="64.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="226"/>
+      <c r="B42" s="227"/>
       <c r="C42" s="9" t="s">
         <v>111</v>
       </c>
       <c r="D42" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="E42" s="251"/>
+      <c r="E42" s="252"/>
       <c r="F42" s="63" t="s">
         <v>54</v>
       </c>
@@ -8027,7 +8034,7 @@
       <c r="Q42" s="66"/>
     </row>
     <row r="43" spans="2:17" ht="64.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B43" s="226"/>
+      <c r="B43" s="227"/>
       <c r="C43" s="120" t="s">
         <v>112</v>
       </c>
@@ -8079,7 +8086,7 @@
       <c r="Q43" s="121"/>
     </row>
     <row r="44" spans="2:17" ht="324.60000000000002" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="226"/>
+      <c r="B44" s="227"/>
       <c r="C44" s="9" t="s">
         <v>98</v>
       </c>
@@ -8132,7 +8139,7 @@
       <c r="Q44" s="68"/>
     </row>
     <row r="45" spans="2:17" ht="97.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B45" s="226"/>
+      <c r="B45" s="227"/>
       <c r="C45" s="35" t="s">
         <v>99</v>
       </c>
@@ -8185,14 +8192,14 @@
       <c r="Q45" s="51"/>
     </row>
     <row r="46" spans="2:17" ht="63.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="226"/>
-      <c r="C46" s="252" t="s">
+      <c r="B46" s="227"/>
+      <c r="C46" s="253" t="s">
         <v>100</v>
       </c>
-      <c r="D46" s="255" t="s">
+      <c r="D46" s="256" t="s">
         <v>62</v>
       </c>
-      <c r="E46" s="247">
+      <c r="E46" s="248">
         <v>1</v>
       </c>
       <c r="F46" s="14" t="s">
@@ -8238,10 +8245,10 @@
       <c r="Q46" s="69"/>
     </row>
     <row r="47" spans="2:17" ht="63.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B47" s="226"/>
-      <c r="C47" s="253"/>
-      <c r="D47" s="256"/>
-      <c r="E47" s="248"/>
+      <c r="B47" s="227"/>
+      <c r="C47" s="254"/>
+      <c r="D47" s="257"/>
+      <c r="E47" s="249"/>
       <c r="F47" s="14" t="s">
         <v>64</v>
       </c>
@@ -8285,10 +8292,10 @@
       <c r="Q47" s="69"/>
     </row>
     <row r="48" spans="2:17" ht="63.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="226"/>
-      <c r="C48" s="254"/>
-      <c r="D48" s="257"/>
-      <c r="E48" s="249"/>
+      <c r="B48" s="227"/>
+      <c r="C48" s="255"/>
+      <c r="D48" s="258"/>
+      <c r="E48" s="250"/>
       <c r="F48" s="14" t="s">
         <v>65</v>
       </c>
@@ -8329,7 +8336,7 @@
       <c r="Q48" s="69"/>
     </row>
     <row r="49" spans="2:17" ht="72" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B49" s="226"/>
+      <c r="B49" s="227"/>
       <c r="C49" s="35" t="s">
         <v>101</v>
       </c>
@@ -8382,7 +8389,7 @@
       <c r="Q49" s="71"/>
     </row>
     <row r="50" spans="2:17" ht="72" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="227"/>
+      <c r="B50" s="228"/>
       <c r="C50" s="9" t="s">
         <v>102</v>
       </c>
@@ -8432,7 +8439,7 @@
       <c r="Q50" s="72"/>
     </row>
     <row r="51" spans="2:17" ht="88.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B51" s="225" t="s">
+      <c r="B51" s="226" t="s">
         <v>69</v>
       </c>
       <c r="C51" s="78" t="s">
@@ -8487,7 +8494,7 @@
       </c>
     </row>
     <row r="52" spans="2:17" ht="93.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="226"/>
+      <c r="B52" s="227"/>
       <c r="C52" s="21" t="s">
         <v>123</v>
       </c>
@@ -8537,7 +8544,7 @@
       <c r="Q52" s="30"/>
     </row>
     <row r="53" spans="2:17" ht="93.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B53" s="226"/>
+      <c r="B53" s="227"/>
       <c r="C53" s="21" t="s">
         <v>123</v>
       </c>
@@ -8587,7 +8594,7 @@
       </c>
     </row>
     <row r="54" spans="2:17" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="226"/>
+      <c r="B54" s="227"/>
       <c r="C54" s="21" t="s">
         <v>113</v>
       </c>
@@ -8635,7 +8642,7 @@
       <c r="Q54" s="76"/>
     </row>
     <row r="55" spans="2:17" s="113" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B55" s="227"/>
+      <c r="B55" s="228"/>
       <c r="C55" s="114" t="s">
         <v>114</v>
       </c>
@@ -10891,7 +10898,9 @@
       <c r="H14" s="148" t="s">
         <v>81</v>
       </c>
-      <c r="I14" s="148"/>
+      <c r="I14" s="148" t="s">
+        <v>646</v>
+      </c>
       <c r="J14" s="148"/>
       <c r="K14" s="148"/>
       <c r="L14" s="148"/>
@@ -11418,7 +11427,9 @@
       <c r="H21" s="148" t="s">
         <v>81</v>
       </c>
-      <c r="I21" s="148"/>
+      <c r="I21" s="148" t="s">
+        <v>646</v>
+      </c>
       <c r="J21" s="148"/>
       <c r="K21" s="148"/>
       <c r="L21" s="148"/>
@@ -11493,7 +11504,9 @@
       <c r="H22" s="148" t="s">
         <v>81</v>
       </c>
-      <c r="I22" s="148"/>
+      <c r="I22" s="148" t="s">
+        <v>646</v>
+      </c>
       <c r="J22" s="148"/>
       <c r="K22" s="148"/>
       <c r="L22" s="148"/>
@@ -11648,7 +11661,9 @@
       <c r="I24" s="148" t="s">
         <v>610</v>
       </c>
-      <c r="J24" s="148"/>
+      <c r="J24" s="148" t="s">
+        <v>647</v>
+      </c>
       <c r="K24" s="148"/>
       <c r="L24" s="148"/>
       <c r="M24" s="148"/>
@@ -11725,7 +11740,9 @@
       <c r="I25" s="148" t="s">
         <v>610</v>
       </c>
-      <c r="J25" s="148"/>
+      <c r="J25" s="148" t="s">
+        <v>647</v>
+      </c>
       <c r="K25" s="148"/>
       <c r="L25" s="148"/>
       <c r="M25" s="148"/>
@@ -13151,7 +13168,9 @@
       <c r="H44" s="148" t="s">
         <v>81</v>
       </c>
-      <c r="I44" s="148"/>
+      <c r="I44" s="148" t="s">
+        <v>646</v>
+      </c>
       <c r="J44" s="148"/>
       <c r="K44" s="148"/>
       <c r="L44" s="148"/>
@@ -13765,7 +13784,9 @@
       <c r="H52" s="148" t="s">
         <v>81</v>
       </c>
-      <c r="I52" s="148"/>
+      <c r="I52" s="148" t="s">
+        <v>646</v>
+      </c>
       <c r="J52" s="148"/>
       <c r="K52" s="148"/>
       <c r="L52" s="148"/>
@@ -14993,7 +15014,9 @@
       <c r="H68" s="148" t="s">
         <v>81</v>
       </c>
-      <c r="I68" s="148"/>
+      <c r="I68" s="148" t="s">
+        <v>646</v>
+      </c>
       <c r="J68" s="148"/>
       <c r="K68" s="148"/>
       <c r="L68" s="148"/>
@@ -15148,7 +15171,9 @@
       <c r="I70" s="148" t="s">
         <v>610</v>
       </c>
-      <c r="J70" s="148"/>
+      <c r="J70" s="148" t="s">
+        <v>647</v>
+      </c>
       <c r="K70" s="148"/>
       <c r="L70" s="148"/>
       <c r="M70" s="148"/>
@@ -15225,7 +15250,9 @@
       <c r="I71" s="148" t="s">
         <v>610</v>
       </c>
-      <c r="J71" s="148"/>
+      <c r="J71" s="148" t="s">
+        <v>647</v>
+      </c>
       <c r="K71" s="148"/>
       <c r="L71" s="148"/>
       <c r="M71" s="148"/>
@@ -16501,7 +16528,9 @@
       <c r="H88" s="148" t="s">
         <v>81</v>
       </c>
-      <c r="I88" s="148"/>
+      <c r="I88" s="148" t="s">
+        <v>646</v>
+      </c>
       <c r="J88" s="148"/>
       <c r="K88" s="148"/>
       <c r="L88" s="148"/>
@@ -17352,7 +17381,9 @@
       <c r="H99" s="148" t="s">
         <v>81</v>
       </c>
-      <c r="I99" s="148"/>
+      <c r="I99" s="148" t="s">
+        <v>646</v>
+      </c>
       <c r="J99" s="148"/>
       <c r="K99" s="148"/>
       <c r="L99" s="148"/>
@@ -18357,7 +18388,9 @@
       <c r="H112" s="148" t="s">
         <v>81</v>
       </c>
-      <c r="I112" s="148"/>
+      <c r="I112" s="148" t="s">
+        <v>646</v>
+      </c>
       <c r="J112" s="148"/>
       <c r="K112" s="148"/>
       <c r="L112" s="148"/>
@@ -18732,7 +18765,9 @@
       <c r="H117" s="148" t="s">
         <v>81</v>
       </c>
-      <c r="I117" s="148"/>
+      <c r="I117" s="148" t="s">
+        <v>646</v>
+      </c>
       <c r="J117" s="148"/>
       <c r="K117" s="148"/>
       <c r="L117" s="148"/>
@@ -19407,7 +19442,9 @@
       <c r="H126" s="148" t="s">
         <v>81</v>
       </c>
-      <c r="I126" s="148"/>
+      <c r="I126" s="148" t="s">
+        <v>646</v>
+      </c>
       <c r="J126" s="148"/>
       <c r="K126" s="148"/>
       <c r="L126" s="148"/>

--- a/doc/SourceData.xlsx
+++ b/doc/SourceData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SourceCode\python\ProductionSimulatorDynamic\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE4E8F7-4715-4742-BEC0-0308A151ECFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{385B0956-8D17-4CB3-A202-F1A392B64AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{42FB03BA-B493-4523-AFA3-A29D55EE9891}"/>
   </bookViews>
@@ -1154,7 +1154,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3446" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3456" uniqueCount="650">
   <si>
     <t>片材長邊尺寸 (mm) mm</t>
   </si>
@@ -3517,6 +3517,14 @@
   </si>
   <si>
     <t>SP0002</t>
+  </si>
+  <si>
+    <t>UPDB002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新機</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -5053,38 +5061,140 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5113,6 +5223,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5122,139 +5235,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6352,21 +6360,21 @@
       </c>
     </row>
     <row r="8" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="G8" s="193" t="s">
+      <c r="G8" s="251" t="s">
         <v>121</v>
       </c>
-      <c r="H8" s="194"/>
-      <c r="I8" s="195"/>
-      <c r="J8" s="196" t="s">
+      <c r="H8" s="252"/>
+      <c r="I8" s="253"/>
+      <c r="J8" s="254" t="s">
         <v>120</v>
       </c>
-      <c r="K8" s="196"/>
-      <c r="L8" s="196"/>
-      <c r="M8" s="197" t="s">
+      <c r="K8" s="254"/>
+      <c r="L8" s="254"/>
+      <c r="M8" s="255" t="s">
         <v>119</v>
       </c>
-      <c r="N8" s="197"/>
-      <c r="O8" s="197"/>
+      <c r="N8" s="255"/>
+      <c r="O8" s="255"/>
       <c r="P8" s="2"/>
     </row>
     <row r="9" spans="2:17" ht="51.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6420,7 +6428,7 @@
       </c>
     </row>
     <row r="10" spans="2:17" ht="106.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="204" t="s">
+      <c r="B10" s="238" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="85" t="s">
@@ -6473,14 +6481,14 @@
       <c r="Q10" s="13"/>
     </row>
     <row r="11" spans="2:17" ht="84.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="205"/>
-      <c r="C11" s="207" t="s">
+      <c r="B11" s="239"/>
+      <c r="C11" s="241" t="s">
         <v>76</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="E11" s="209">
+      <c r="E11" s="243">
         <v>1</v>
       </c>
       <c r="F11" s="14" t="s">
@@ -6526,12 +6534,12 @@
       <c r="Q11" s="19"/>
     </row>
     <row r="12" spans="2:17" ht="86.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="205"/>
-      <c r="C12" s="208"/>
+      <c r="B12" s="239"/>
+      <c r="C12" s="242"/>
       <c r="D12" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="E12" s="210"/>
+      <c r="E12" s="244"/>
       <c r="F12" s="14" t="s">
         <v>14</v>
       </c>
@@ -6575,14 +6583,14 @@
       <c r="Q12" s="19"/>
     </row>
     <row r="13" spans="2:17" ht="90.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="205"/>
-      <c r="C13" s="211" t="s">
+      <c r="B13" s="239"/>
+      <c r="C13" s="245" t="s">
         <v>109</v>
       </c>
       <c r="D13" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="213">
+      <c r="E13" s="248">
         <v>3</v>
       </c>
       <c r="F13" s="20" t="s">
@@ -6613,16 +6621,16 @@
         <f t="shared" ref="O13:O25" si="1">M13*N13/60</f>
         <v>12</v>
       </c>
-      <c r="P13" s="216"/>
-      <c r="Q13" s="217"/>
+      <c r="P13" s="224"/>
+      <c r="Q13" s="230"/>
     </row>
     <row r="14" spans="2:17" ht="90.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="205"/>
-      <c r="C14" s="212"/>
+      <c r="B14" s="239"/>
+      <c r="C14" s="246"/>
       <c r="D14" s="42" t="s">
         <v>474</v>
       </c>
-      <c r="E14" s="214"/>
+      <c r="E14" s="249"/>
       <c r="F14" s="20"/>
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
@@ -6642,16 +6650,16 @@
       <c r="M14" s="9"/>
       <c r="N14" s="10"/>
       <c r="O14" s="11"/>
-      <c r="P14" s="216"/>
-      <c r="Q14" s="217"/>
+      <c r="P14" s="224"/>
+      <c r="Q14" s="230"/>
     </row>
     <row r="15" spans="2:17" ht="90.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="205"/>
-      <c r="C15" s="201"/>
+      <c r="B15" s="239"/>
+      <c r="C15" s="247"/>
       <c r="D15" s="98" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="215"/>
+      <c r="E15" s="250"/>
       <c r="F15" s="20" t="s">
         <v>18</v>
       </c>
@@ -6689,11 +6697,11 @@
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="P15" s="216"/>
-      <c r="Q15" s="217"/>
+      <c r="P15" s="224"/>
+      <c r="Q15" s="230"/>
     </row>
     <row r="16" spans="2:17" ht="100.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="205"/>
+      <c r="B16" s="239"/>
       <c r="C16" s="21" t="s">
         <v>79</v>
       </c>
@@ -6743,7 +6751,7 @@
       </c>
     </row>
     <row r="17" spans="2:18" ht="98.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="206"/>
+      <c r="B17" s="240"/>
       <c r="C17" s="105" t="s">
         <v>80</v>
       </c>
@@ -6798,7 +6806,7 @@
       <c r="Q17" s="31"/>
     </row>
     <row r="18" spans="2:18" ht="122.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="226" t="s">
+      <c r="B18" s="193" t="s">
         <v>21</v>
       </c>
       <c r="C18" s="10" t="s">
@@ -6853,7 +6861,7 @@
       <c r="Q18" s="34"/>
     </row>
     <row r="19" spans="2:18" ht="57" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="227"/>
+      <c r="B19" s="194"/>
       <c r="C19" s="35" t="s">
         <v>83</v>
       </c>
@@ -6907,14 +6915,14 @@
       <c r="R19" s="37"/>
     </row>
     <row r="20" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="227"/>
+      <c r="B20" s="194"/>
       <c r="C20" s="10" t="s">
         <v>105</v>
       </c>
       <c r="D20" s="88" t="s">
         <v>106</v>
       </c>
-      <c r="E20" s="218">
+      <c r="E20" s="231">
         <v>1</v>
       </c>
       <c r="F20" s="38" t="s">
@@ -6956,19 +6964,19 @@
         <f t="shared" si="1"/>
         <v>1.25</v>
       </c>
-      <c r="P20" s="221"/>
-      <c r="Q20" s="223"/>
+      <c r="P20" s="233"/>
+      <c r="Q20" s="235"/>
       <c r="R20" s="41"/>
     </row>
     <row r="21" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="227"/>
+      <c r="B21" s="194"/>
       <c r="C21" s="10" t="s">
         <v>105</v>
       </c>
       <c r="D21" s="110" t="s">
         <v>132</v>
       </c>
-      <c r="E21" s="219"/>
+      <c r="E21" s="232"/>
       <c r="F21" s="20" t="s">
         <v>25</v>
       </c>
@@ -6999,19 +7007,19 @@
         <f>M21*N21/60</f>
         <v>1.25</v>
       </c>
-      <c r="P21" s="216"/>
-      <c r="Q21" s="224"/>
+      <c r="P21" s="224"/>
+      <c r="Q21" s="236"/>
       <c r="R21" s="41"/>
     </row>
     <row r="22" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="227"/>
+      <c r="B22" s="194"/>
       <c r="C22" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="229" t="s">
+      <c r="D22" s="210" t="s">
         <v>107</v>
       </c>
-      <c r="E22" s="219"/>
+      <c r="E22" s="232"/>
       <c r="F22" s="43" t="s">
         <v>26</v>
       </c>
@@ -7051,17 +7059,17 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="P22" s="216"/>
-      <c r="Q22" s="224"/>
+      <c r="P22" s="224"/>
+      <c r="Q22" s="236"/>
       <c r="R22" s="41"/>
     </row>
     <row r="23" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="227"/>
+      <c r="B23" s="194"/>
       <c r="C23" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D23" s="230"/>
-      <c r="E23" s="220"/>
+      <c r="D23" s="211"/>
+      <c r="E23" s="217"/>
       <c r="F23" s="47" t="s">
         <v>24</v>
       </c>
@@ -7101,12 +7109,12 @@
         <f t="shared" si="1"/>
         <v>1.25</v>
       </c>
-      <c r="P23" s="222"/>
-      <c r="Q23" s="225"/>
+      <c r="P23" s="234"/>
+      <c r="Q23" s="237"/>
       <c r="R23" s="41"/>
     </row>
     <row r="24" spans="2:18" ht="133.19999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="228"/>
+      <c r="B24" s="195"/>
       <c r="C24" s="91" t="s">
         <v>84</v>
       </c>
@@ -7160,29 +7168,29 @@
       <c r="R24" s="49"/>
     </row>
     <row r="25" spans="2:18" ht="129" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="233" t="s">
+      <c r="B25" s="214" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="240" t="s">
+      <c r="C25" s="200" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="240" t="s">
+      <c r="D25" s="200" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="241">
+      <c r="E25" s="222">
         <v>1</v>
       </c>
       <c r="F25" s="50" t="s">
         <v>140</v>
       </c>
-      <c r="G25" s="202">
+      <c r="G25" s="259">
         <f>90/4</f>
         <v>22.5</v>
       </c>
-      <c r="H25" s="200">
+      <c r="H25" s="258">
         <v>8</v>
       </c>
-      <c r="I25" s="198">
+      <c r="I25" s="256">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
@@ -7198,14 +7206,14 @@
         <f t="shared" si="4"/>
         <v>3.75</v>
       </c>
-      <c r="M25" s="198">
+      <c r="M25" s="256">
         <f>90/5</f>
         <v>18</v>
       </c>
-      <c r="N25" s="200">
+      <c r="N25" s="258">
         <v>10</v>
       </c>
-      <c r="O25" s="198">
+      <c r="O25" s="256">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -7213,16 +7221,16 @@
       <c r="Q25" s="51"/>
     </row>
     <row r="26" spans="2:18" ht="136.19999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="233"/>
-      <c r="C26" s="240"/>
-      <c r="D26" s="240"/>
-      <c r="E26" s="242"/>
+      <c r="B26" s="214"/>
+      <c r="C26" s="200"/>
+      <c r="D26" s="200"/>
+      <c r="E26" s="223"/>
       <c r="F26" s="48" t="s">
         <v>141</v>
       </c>
-      <c r="G26" s="203"/>
-      <c r="H26" s="201"/>
-      <c r="I26" s="199"/>
+      <c r="G26" s="260"/>
+      <c r="H26" s="247"/>
+      <c r="I26" s="257"/>
       <c r="J26" s="15">
         <f>110/4</f>
         <v>27.5</v>
@@ -7235,21 +7243,21 @@
         <f t="shared" ref="L26" si="7">J26*K26/60</f>
         <v>4.583333333333333</v>
       </c>
-      <c r="M26" s="199"/>
-      <c r="N26" s="201"/>
-      <c r="O26" s="199"/>
+      <c r="M26" s="257"/>
+      <c r="N26" s="247"/>
+      <c r="O26" s="257"/>
       <c r="P26" s="140"/>
       <c r="Q26" s="23"/>
     </row>
     <row r="27" spans="2:18" ht="73.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="233"/>
+      <c r="B27" s="214"/>
       <c r="C27" s="141" t="s">
         <v>139</v>
       </c>
-      <c r="D27" s="234" t="s">
+      <c r="D27" s="215" t="s">
         <v>90</v>
       </c>
-      <c r="E27" s="235">
+      <c r="E27" s="216">
         <v>1</v>
       </c>
       <c r="F27" s="47" t="s">
@@ -7291,16 +7299,16 @@
         <f>M27*N27/60</f>
         <v>0.8666666666666667</v>
       </c>
-      <c r="P27" s="236"/>
-      <c r="Q27" s="231"/>
+      <c r="P27" s="218"/>
+      <c r="Q27" s="212"/>
     </row>
     <row r="28" spans="2:18" ht="73.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="233"/>
+      <c r="B28" s="214"/>
       <c r="C28" s="52" t="s">
         <v>138</v>
       </c>
-      <c r="D28" s="230"/>
-      <c r="E28" s="220"/>
+      <c r="D28" s="211"/>
+      <c r="E28" s="217"/>
       <c r="F28" s="32" t="s">
         <v>89</v>
       </c>
@@ -7337,11 +7345,11 @@
         <f>M28*N28/60</f>
         <v>13</v>
       </c>
-      <c r="P28" s="237"/>
-      <c r="Q28" s="232"/>
+      <c r="P28" s="219"/>
+      <c r="Q28" s="213"/>
     </row>
     <row r="29" spans="2:18" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="233"/>
+      <c r="B29" s="214"/>
       <c r="C29" s="35" t="s">
         <v>91</v>
       </c>
@@ -7394,7 +7402,7 @@
       <c r="Q29" s="31"/>
     </row>
     <row r="30" spans="2:18" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="233"/>
+      <c r="B30" s="214"/>
       <c r="C30" s="55" t="s">
         <v>92</v>
       </c>
@@ -7447,14 +7455,14 @@
       <c r="Q30" s="58"/>
     </row>
     <row r="31" spans="2:18" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="233"/>
-      <c r="C31" s="251" t="s">
+      <c r="B31" s="214"/>
+      <c r="C31" s="199" t="s">
         <v>93</v>
       </c>
-      <c r="D31" s="240" t="s">
+      <c r="D31" s="200" t="s">
         <v>32</v>
       </c>
-      <c r="E31" s="248">
+      <c r="E31" s="196">
         <v>1</v>
       </c>
       <c r="F31" s="14" t="s">
@@ -7494,10 +7502,10 @@
       <c r="Q31" s="60"/>
     </row>
     <row r="32" spans="2:18" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="233"/>
-      <c r="C32" s="251"/>
-      <c r="D32" s="240"/>
-      <c r="E32" s="249"/>
+      <c r="B32" s="214"/>
+      <c r="C32" s="199"/>
+      <c r="D32" s="200"/>
+      <c r="E32" s="197"/>
       <c r="F32" s="14" t="s">
         <v>34</v>
       </c>
@@ -7535,10 +7543,10 @@
       <c r="Q32" s="60"/>
     </row>
     <row r="33" spans="2:17" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="233"/>
-      <c r="C33" s="251"/>
-      <c r="D33" s="240"/>
-      <c r="E33" s="250"/>
+      <c r="B33" s="214"/>
+      <c r="C33" s="199"/>
+      <c r="D33" s="200"/>
+      <c r="E33" s="198"/>
       <c r="F33" s="14" t="s">
         <v>35</v>
       </c>
@@ -7576,14 +7584,14 @@
       <c r="Q33" s="60"/>
     </row>
     <row r="34" spans="2:17" ht="52.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="233"/>
-      <c r="C34" s="251" t="s">
+      <c r="B34" s="214"/>
+      <c r="C34" s="199" t="s">
         <v>96</v>
       </c>
-      <c r="D34" s="240" t="s">
+      <c r="D34" s="200" t="s">
         <v>36</v>
       </c>
-      <c r="E34" s="252">
+      <c r="E34" s="201">
         <v>1</v>
       </c>
       <c r="F34" s="61" t="s">
@@ -7622,10 +7630,10 @@
       <c r="Q34" s="31"/>
     </row>
     <row r="35" spans="2:17" ht="52.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="233"/>
-      <c r="C35" s="251"/>
-      <c r="D35" s="240"/>
-      <c r="E35" s="252"/>
+      <c r="B35" s="214"/>
+      <c r="C35" s="199"/>
+      <c r="D35" s="200"/>
+      <c r="E35" s="201"/>
       <c r="F35" s="61" t="s">
         <v>135</v>
       </c>
@@ -7666,7 +7674,7 @@
       <c r="Q35" s="31"/>
     </row>
     <row r="36" spans="2:17" s="113" customFormat="1" ht="90.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="233"/>
+      <c r="B36" s="214"/>
       <c r="C36" s="192" t="s">
         <v>645</v>
       </c>
@@ -7716,14 +7724,14 @@
       <c r="Q36" s="126"/>
     </row>
     <row r="37" spans="2:17" ht="81" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="233"/>
-      <c r="C37" s="259" t="s">
+      <c r="B37" s="214"/>
+      <c r="C37" s="208" t="s">
         <v>109</v>
       </c>
       <c r="D37" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="E37" s="238">
+      <c r="E37" s="220">
         <v>3</v>
       </c>
       <c r="F37" s="56" t="s">
@@ -7765,18 +7773,18 @@
         <f>M37*N37/60</f>
         <v>12.5</v>
       </c>
-      <c r="P37" s="216"/>
-      <c r="Q37" s="244" t="s">
+      <c r="P37" s="224"/>
+      <c r="Q37" s="226" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="38" spans="2:17" ht="81" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="233"/>
-      <c r="C38" s="260"/>
+      <c r="B38" s="214"/>
+      <c r="C38" s="209"/>
       <c r="D38" s="88" t="s">
         <v>42</v>
       </c>
-      <c r="E38" s="239"/>
+      <c r="E38" s="221"/>
       <c r="F38" s="56" t="s">
         <v>43</v>
       </c>
@@ -7816,18 +7824,18 @@
         <f>M38*N38/60</f>
         <v>5</v>
       </c>
-      <c r="P38" s="216"/>
-      <c r="Q38" s="245"/>
+      <c r="P38" s="224"/>
+      <c r="Q38" s="227"/>
     </row>
     <row r="39" spans="2:17" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="233"/>
+      <c r="B39" s="214"/>
       <c r="C39" s="62" t="s">
         <v>103</v>
       </c>
       <c r="D39" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="E39" s="239"/>
+      <c r="E39" s="221"/>
       <c r="F39" s="56" t="s">
         <v>45</v>
       </c>
@@ -7867,20 +7875,20 @@
         <f>M39*N39/60</f>
         <v>1.25</v>
       </c>
-      <c r="P39" s="216"/>
-      <c r="Q39" s="246" t="s">
+      <c r="P39" s="224"/>
+      <c r="Q39" s="228" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="40" spans="2:17" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="233"/>
+      <c r="B40" s="214"/>
       <c r="C40" s="55" t="s">
         <v>103</v>
       </c>
       <c r="D40" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="E40" s="239"/>
+      <c r="E40" s="221"/>
       <c r="F40" s="56" t="s">
         <v>48</v>
       </c>
@@ -7920,11 +7928,11 @@
         <f>M40*N40/60</f>
         <v>0.625</v>
       </c>
-      <c r="P40" s="243"/>
-      <c r="Q40" s="247"/>
+      <c r="P40" s="225"/>
+      <c r="Q40" s="229"/>
     </row>
     <row r="41" spans="2:17" ht="64.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="226" t="s">
+      <c r="B41" s="193" t="s">
         <v>49</v>
       </c>
       <c r="C41" s="9" t="s">
@@ -7933,7 +7941,7 @@
       <c r="D41" s="94" t="s">
         <v>50</v>
       </c>
-      <c r="E41" s="252">
+      <c r="E41" s="201">
         <v>2</v>
       </c>
       <c r="F41" s="63" t="s">
@@ -7981,14 +7989,14 @@
       <c r="Q41" s="59"/>
     </row>
     <row r="42" spans="2:17" ht="64.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="227"/>
+      <c r="B42" s="194"/>
       <c r="C42" s="9" t="s">
         <v>111</v>
       </c>
       <c r="D42" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="E42" s="252"/>
+      <c r="E42" s="201"/>
       <c r="F42" s="63" t="s">
         <v>54</v>
       </c>
@@ -8034,7 +8042,7 @@
       <c r="Q42" s="66"/>
     </row>
     <row r="43" spans="2:17" ht="64.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B43" s="227"/>
+      <c r="B43" s="194"/>
       <c r="C43" s="120" t="s">
         <v>112</v>
       </c>
@@ -8086,7 +8094,7 @@
       <c r="Q43" s="121"/>
     </row>
     <row r="44" spans="2:17" ht="324.60000000000002" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="227"/>
+      <c r="B44" s="194"/>
       <c r="C44" s="9" t="s">
         <v>98</v>
       </c>
@@ -8139,7 +8147,7 @@
       <c r="Q44" s="68"/>
     </row>
     <row r="45" spans="2:17" ht="97.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B45" s="227"/>
+      <c r="B45" s="194"/>
       <c r="C45" s="35" t="s">
         <v>99</v>
       </c>
@@ -8192,14 +8200,14 @@
       <c r="Q45" s="51"/>
     </row>
     <row r="46" spans="2:17" ht="63.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="227"/>
-      <c r="C46" s="253" t="s">
+      <c r="B46" s="194"/>
+      <c r="C46" s="202" t="s">
         <v>100</v>
       </c>
-      <c r="D46" s="256" t="s">
+      <c r="D46" s="205" t="s">
         <v>62</v>
       </c>
-      <c r="E46" s="248">
+      <c r="E46" s="196">
         <v>1</v>
       </c>
       <c r="F46" s="14" t="s">
@@ -8245,10 +8253,10 @@
       <c r="Q46" s="69"/>
     </row>
     <row r="47" spans="2:17" ht="63.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B47" s="227"/>
-      <c r="C47" s="254"/>
-      <c r="D47" s="257"/>
-      <c r="E47" s="249"/>
+      <c r="B47" s="194"/>
+      <c r="C47" s="203"/>
+      <c r="D47" s="206"/>
+      <c r="E47" s="197"/>
       <c r="F47" s="14" t="s">
         <v>64</v>
       </c>
@@ -8292,10 +8300,10 @@
       <c r="Q47" s="69"/>
     </row>
     <row r="48" spans="2:17" ht="63.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="227"/>
-      <c r="C48" s="255"/>
-      <c r="D48" s="258"/>
-      <c r="E48" s="250"/>
+      <c r="B48" s="194"/>
+      <c r="C48" s="204"/>
+      <c r="D48" s="207"/>
+      <c r="E48" s="198"/>
       <c r="F48" s="14" t="s">
         <v>65</v>
       </c>
@@ -8336,7 +8344,7 @@
       <c r="Q48" s="69"/>
     </row>
     <row r="49" spans="2:17" ht="72" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B49" s="227"/>
+      <c r="B49" s="194"/>
       <c r="C49" s="35" t="s">
         <v>101</v>
       </c>
@@ -8389,7 +8397,7 @@
       <c r="Q49" s="71"/>
     </row>
     <row r="50" spans="2:17" ht="72" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="228"/>
+      <c r="B50" s="195"/>
       <c r="C50" s="9" t="s">
         <v>102</v>
       </c>
@@ -8439,7 +8447,7 @@
       <c r="Q50" s="72"/>
     </row>
     <row r="51" spans="2:17" ht="88.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B51" s="226" t="s">
+      <c r="B51" s="193" t="s">
         <v>69</v>
       </c>
       <c r="C51" s="78" t="s">
@@ -8494,7 +8502,7 @@
       </c>
     </row>
     <row r="52" spans="2:17" ht="93.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="227"/>
+      <c r="B52" s="194"/>
       <c r="C52" s="21" t="s">
         <v>123</v>
       </c>
@@ -8544,7 +8552,7 @@
       <c r="Q52" s="30"/>
     </row>
     <row r="53" spans="2:17" ht="93.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B53" s="227"/>
+      <c r="B53" s="194"/>
       <c r="C53" s="21" t="s">
         <v>123</v>
       </c>
@@ -8594,7 +8602,7 @@
       </c>
     </row>
     <row r="54" spans="2:17" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="227"/>
+      <c r="B54" s="194"/>
       <c r="C54" s="21" t="s">
         <v>113</v>
       </c>
@@ -8642,7 +8650,7 @@
       <c r="Q54" s="76"/>
     </row>
     <row r="55" spans="2:17" s="113" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B55" s="228"/>
+      <c r="B55" s="195"/>
       <c r="C55" s="114" t="s">
         <v>114</v>
       </c>
@@ -8695,18 +8703,25 @@
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="B51:B55"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="M25:M26"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="O25:O26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="B10:B17"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="P13:P15"/>
+    <mergeCell ref="Q13:Q15"/>
+    <mergeCell ref="E20:E23"/>
+    <mergeCell ref="P20:P23"/>
+    <mergeCell ref="Q20:Q23"/>
     <mergeCell ref="B18:B24"/>
     <mergeCell ref="B41:B50"/>
     <mergeCell ref="D22:D23"/>
@@ -8722,25 +8737,18 @@
     <mergeCell ref="P37:P40"/>
     <mergeCell ref="Q37:Q38"/>
     <mergeCell ref="Q39:Q40"/>
-    <mergeCell ref="P13:P15"/>
-    <mergeCell ref="Q13:Q15"/>
-    <mergeCell ref="E20:E23"/>
-    <mergeCell ref="P20:P23"/>
-    <mergeCell ref="Q20:Q23"/>
-    <mergeCell ref="B10:B17"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="M25:M26"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="O25:O26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="B51:B55"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="C37:C38"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10032,7 +10040,7 @@
         <v>163</v>
       </c>
       <c r="C3" s="181" t="s">
-        <v>168</v>
+        <v>648</v>
       </c>
       <c r="D3" s="184" t="s">
         <v>169</v>
@@ -10132,7 +10140,9 @@
       <c r="H4" s="148" t="s">
         <v>619</v>
       </c>
-      <c r="I4" s="148"/>
+      <c r="I4" s="148" t="s">
+        <v>649</v>
+      </c>
       <c r="J4" s="148"/>
       <c r="K4" s="148"/>
       <c r="L4" s="148"/>
@@ -10671,7 +10681,9 @@
       <c r="H11" s="148" t="s">
         <v>619</v>
       </c>
-      <c r="I11" s="154"/>
+      <c r="I11" s="148" t="s">
+        <v>649</v>
+      </c>
       <c r="J11" s="154"/>
       <c r="K11" s="154"/>
       <c r="L11" s="154"/>
@@ -11127,7 +11139,9 @@
       <c r="H17" s="148" t="s">
         <v>619</v>
       </c>
-      <c r="I17" s="148"/>
+      <c r="I17" s="148" t="s">
+        <v>649</v>
+      </c>
       <c r="J17" s="148"/>
       <c r="K17" s="148"/>
       <c r="L17" s="148"/>
@@ -12643,7 +12657,9 @@
       <c r="H37" s="148" t="s">
         <v>619</v>
       </c>
-      <c r="I37" s="148"/>
+      <c r="I37" s="148" t="s">
+        <v>649</v>
+      </c>
       <c r="J37" s="148"/>
       <c r="K37" s="148"/>
       <c r="L37" s="148"/>
@@ -12718,7 +12734,9 @@
       <c r="H38" s="148" t="s">
         <v>619</v>
       </c>
-      <c r="I38" s="148"/>
+      <c r="I38" s="148" t="s">
+        <v>649</v>
+      </c>
       <c r="J38" s="148"/>
       <c r="K38" s="148"/>
       <c r="L38" s="148"/>
@@ -13557,7 +13575,9 @@
       <c r="H49" s="148" t="s">
         <v>619</v>
       </c>
-      <c r="I49" s="148"/>
+      <c r="I49" s="148" t="s">
+        <v>649</v>
+      </c>
       <c r="J49" s="148"/>
       <c r="K49" s="148"/>
       <c r="L49" s="148"/>
@@ -14325,7 +14345,9 @@
       <c r="H59" s="148" t="s">
         <v>619</v>
       </c>
-      <c r="I59" s="148"/>
+      <c r="I59" s="148" t="s">
+        <v>649</v>
+      </c>
       <c r="J59" s="148"/>
       <c r="K59" s="148"/>
       <c r="L59" s="148"/>
@@ -14789,7 +14811,9 @@
       <c r="H65" s="148" t="s">
         <v>619</v>
       </c>
-      <c r="I65" s="148"/>
+      <c r="I65" s="148" t="s">
+        <v>649</v>
+      </c>
       <c r="J65" s="148"/>
       <c r="K65" s="148"/>
       <c r="L65" s="148"/>
@@ -16153,7 +16177,9 @@
       <c r="H83" s="148" t="s">
         <v>619</v>
       </c>
-      <c r="I83" s="148"/>
+      <c r="I83" s="148" t="s">
+        <v>649</v>
+      </c>
       <c r="J83" s="148"/>
       <c r="K83" s="148"/>
       <c r="L83" s="148"/>
@@ -16228,7 +16254,9 @@
       <c r="H84" s="148" t="s">
         <v>619</v>
       </c>
-      <c r="I84" s="148"/>
+      <c r="I84" s="148" t="s">
+        <v>649</v>
+      </c>
       <c r="J84" s="148"/>
       <c r="K84" s="148"/>
       <c r="L84" s="148"/>
